--- a/output/amkr_indicator_data.xlsx
+++ b/output/amkr_indicator_data.xlsx
@@ -1706,7 +1706,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>TWSE:t187ap05_L</t>
+          <t>FinMind:TaiwanStockMonthRevenue</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>FinMind:TaiwanStockMonthRevenue</t>
+          <t>TWSE:t187ap05_L</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TWSE:t187ap05_L</t>
+          <t>FinMind:TaiwanStockMonthRevenue</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6496,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>FinMind:TaiwanStockMonthRevenue</t>
+          <t>TWSE:t187ap05_L</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8876,12 +8876,12 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>TWSE:t187ap05_L</t>
+          <t>FinMind:TaiwanStockMonthRevenue</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>FinMind:TaiwanStockMonthRevenue</t>
+          <t>TWSE:t187ap05_L</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>TWSE:t187ap05_L</t>
+          <t>FinMind:TaiwanStockMonthRevenue</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13741,12 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>FinMind:TaiwanStockMonthRevenue</t>
+          <t>TWSE:t187ap05_L</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13956,7 +13956,7 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14656,7 +14656,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14831,7 +14831,7 @@
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15006,7 +15006,7 @@
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -16121,12 +16121,12 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>TWSE:t187ap05_L</t>
+          <t>FinMind:TaiwanStockMonthRevenue</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -16156,12 +16156,12 @@
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>FinMind:TaiwanStockMonthRevenue</t>
+          <t>TWSE:t187ap05_L</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -22319,7 +22319,7 @@
         <v>0.3699436303194559</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1985206859207439</v>
+        <v>0.1985206859207438</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1511.392</v>
@@ -22331,7 +22331,7 @@
         <v>1811.434576535125</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1900.391475374194</v>
+        <v>1900.391475374193</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>1750</v>
@@ -22351,7 +22351,7 @@
         <v/>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>0.6681067953932439</v>
+        <v>0.668106795393244</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>0.0699336938382162</v>
